--- a/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_02_workbook.xlsx
+++ b/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_02_workbook.xlsx
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102973256</v>
+        <v>96772848</v>
       </c>
     </row>
     <row r="4">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1435751.875</v>
+        <v>7636160.5</v>
       </c>
     </row>
     <row r="5">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33591128</v>
+        <v>28612740</v>
       </c>
     </row>
     <row r="6">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9961734693877551</v>
+        <v>0.9438775510204082</v>
       </c>
     </row>
     <row r="7">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>781*Assumptions!$B$3</f>
+        <f>740*Assumptions!$B$3</f>
         <v/>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>RandomForest meets the deployment-readiness bar</t>
+          <t>CatBoost meets the deployment-readiness bar</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Holdout ROC-AUC 0.7420 with a 95% bootstrap CI of [0.7089, 0.7761]; deployment checks 3/3 PASS.</t>
+          <t>Holdout ROC-AUC 0.7520 with a 95% bootstrap CI of [0.7209, 0.7828]; deployment checks 3/3 PASS.</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Calibration gap 0.0721 vs. &lt;0.1 threshold; split-half PSI 0.0093 vs. &lt;0.1 threshold.</t>
+          <t>Calibration gap 0.0386 vs. &lt;0.1 threshold; split-half PSI 0.0162 vs. &lt;0.1 threshold.</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Champion mean CV ROC-AUC: 0.7158.</t>
+          <t>Champion mean CV ROC-AUC: 0.7145.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>$33,591,128 of real holdout volume is on applications the model flags as approvable but that were really declined (false positives).</t>
+          <t>$28,612,740 of real holdout volume is on applications the model flags as approvable but that were really declined (false positives).</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Wrongly-flagged volume is 0.33x the real correctly-approved volume — track this ratio on every run.</t>
+          <t>Wrongly-flagged volume is 0.30x the real correctly-approved volume — track this ratio on every run.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>UPSTREAM_PD_FROM_NB01 (from Notebook 01's champion, XGBoost) matched 7,000 / 7,000 real in-scope rows (100.00%) and ranks #23 of 48 real features by mean |SHAP|.</t>
+          <t>UPSTREAM_PD_FROM_NB01 (from Notebook 01's champion, XGBoost) matched 7,000 / 7,000 real in-scope rows (100.00%) and ranks #14 of 48 real features by mean |SHAP|.</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Champion mean CV ROC-AUC with this feature included: 0.7158.</t>
+          <t>Champion mean CV ROC-AUC with this feature included: 0.7145.</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6906449816696502</v>
+        <v>0.6899461487579833</v>
       </c>
       <c r="C2" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6695155630463137</v>
+        <v>0.6757041582426782</v>
       </c>
       <c r="C3" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6825729009787398</v>
+        <v>0.6859026342637404</v>
       </c>
       <c r="C4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.671163612854041</v>
+        <v>0.6767879098169207</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7157777583104662</v>
+        <v>0.7140993440510668</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01544723957292945</v>
+        <v>0.01754291480623798</v>
       </c>
     </row>
     <row r="3">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7110685704583318</v>
+        <v>0.7144617076753196</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008889015330393775</v>
+        <v>0.006884800015305738</v>
       </c>
     </row>
   </sheetData>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7016516853932584</v>
+        <v>0.6937977528089887</v>
       </c>
     </row>
     <row r="3">
@@ -1518,7 +1518,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7111727313155624</v>
+        <v>0.7127348284122292</v>
       </c>
     </row>
     <row r="4">
@@ -1531,7 +1531,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6995130592064696</v>
+        <v>0.6964822918729843</v>
       </c>
     </row>
     <row r="5">
@@ -1544,7 +1544,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7263676758013221</v>
+        <v>0.7291144254808681</v>
       </c>
     </row>
     <row r="6">
@@ -1557,7 +1557,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7401836398357182</v>
+        <v>0.7383674216802635</v>
       </c>
     </row>
     <row r="7">
@@ -1570,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7090636704119849</v>
+        <v>0.7121722846441948</v>
       </c>
     </row>
     <row r="8">
@@ -1583,7 +1583,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7018337824051064</v>
+        <v>0.709569526400562</v>
       </c>
     </row>
     <row r="9">
@@ -1596,7 +1596,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7026858353669246</v>
+        <v>0.7094611512431377</v>
       </c>
     </row>
     <row r="10">
@@ -1609,7 +1609,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7162439412681388</v>
+        <v>0.713183277339502</v>
       </c>
     </row>
     <row r="11">
@@ -1622,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7255156228395039</v>
+        <v>0.7279222987492012</v>
       </c>
     </row>
   </sheetData>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7420160733466319</v>
+        <v>0.7519756022709836</v>
       </c>
     </row>
     <row r="3">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7509615384615385</v>
+        <v>0.7676348547717843</v>
       </c>
     </row>
     <row r="4">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9961734693877551</v>
+        <v>0.9438775510204082</v>
       </c>
     </row>
     <row r="5">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.856359649122807</v>
+        <v>0.8466819221967964</v>
       </c>
     </row>
     <row r="6">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1677093421821291</v>
+        <v>0.1627905273362256</v>
       </c>
     </row>
   </sheetData>
@@ -1770,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5847747872128146</v>
+        <v>0.4432606075342877</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5047619047619047</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="D2" t="n">
         <v>105</v>
@@ -1784,10 +1784,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6418738930239659</v>
+        <v>0.5630425452390851</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="D3" t="n">
         <v>105</v>
@@ -1798,10 +1798,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6699238845645153</v>
+        <v>0.6359624468833034</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5904761904761905</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
         <v>105</v>
@@ -1812,10 +1812,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.712820955836591</v>
+        <v>0.708739665602115</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6761904761904762</v>
       </c>
       <c r="D5" t="n">
         <v>105</v>
@@ -1826,10 +1826,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7587480665884867</v>
+        <v>0.7720694893327201</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7047619047619048</v>
       </c>
       <c r="D6" t="n">
         <v>105</v>
@@ -1840,10 +1840,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7941895109954714</v>
+        <v>0.8248801880328871</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="n">
         <v>105</v>
@@ -1854,10 +1854,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8204853403833409</v>
+        <v>0.8727231962703885</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9238095238095239</v>
+        <v>0.8952380952380953</v>
       </c>
       <c r="D8" t="n">
         <v>105</v>
@@ -1868,10 +1868,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8346303660676696</v>
+        <v>0.9040897312649063</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="D9" t="n">
         <v>105</v>
@@ -1882,7 +1882,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8446836450770205</v>
+        <v>0.9240388060776337</v>
       </c>
       <c r="C10" t="n">
         <v>0.9238095238095239</v>
@@ -1896,10 +1896,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8578708020780544</v>
+        <v>0.9461177497369697</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8952380952380953</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="D11" t="n">
         <v>105</v>
@@ -1957,47 +1957,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07739566071397777</v>
+        <v>0.8234520280464654</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMT_GOODS_PRICE</t>
+          <t>AMT_ANNUITY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004739353751590682</v>
+        <v>0.04735754217736185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMT_APPLICATION</t>
+          <t>HOUR_APPR_PROCESS_START</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004612968658838663</v>
+        <v>0.04051760976753375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMT_CREDIT</t>
+          <t>AMT_GOODS_PRICE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004322443314037125</v>
+        <v>0.03904453101962344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMT_ANNUITY</t>
+          <t>AMT_CREDIT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004291840003296307</v>
+        <v>0.03814277933835274</v>
       </c>
     </row>
     <row r="7">
@@ -2007,427 +2007,427 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003484161668837814</v>
+        <v>0.03743063174642171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INSTAL_CNT_PAYMENTS</t>
+          <t>EXT_SOURCE_2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002763828556946299</v>
+        <v>0.03721745772952965</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INSTAL_MEAN_PAYMENT_RATIO</t>
+          <t>APPLICANT_AGE_YEARS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002601572003159998</v>
+        <v>0.0371328823498941</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INSTAL_MEAN_DAYS_LATE_WHEN_LATE</t>
+          <t>CNT_PAYMENT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002218499493517323</v>
+        <v>0.03340609214326563</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CNT_PAYMENT</t>
+          <t>BUREAU_DEBT_TO_CREDIT_RATIO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.002168549239915122</v>
+        <v>0.03267381214222331</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMT_INCOME_TOTAL</t>
+          <t>DAYS_DECISION</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002063201187229597</v>
+        <v>0.03163449959467626</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL</t>
+          <t>NAME_FAMILY_STATUS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.001909263709232732</v>
+        <v>0.03043126017609895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APPLICANT_AGE_YEARS</t>
+          <t>INSTAL_MEAN_PAYMENT_RATIO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.001897654352962206</v>
+        <v>0.02979094807622734</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HOUR_APPR_PROCESS_START</t>
+          <t>UPSTREAM_PD_FROM_NB01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0018000313958536</v>
+        <v>0.02955634431883195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BUREAU_DEBT_TO_CREDIT_RATIO</t>
+          <t>INSTAL_PCT_LATE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.001780265271044291</v>
+        <v>0.02868818692440369</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POS_MEAN_SK_DPD_DEF</t>
+          <t>INSTAL_CNT_PAYMENTS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001692260746182823</v>
+        <v>0.02772881377168427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INSTAL_PCT_LATE</t>
+          <t>POS_CNT_COMPLETED</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.001616687057250245</v>
+        <v>0.02768306011049584</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DAYS_DECISION</t>
+          <t>POS_MEAN_SK_DPD_DEF</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.001513687157601687</v>
+        <v>0.02700045740314979</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMT_DOWN_PAYMENT</t>
+          <t>AMT_APPLICATION</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.001504518030667069</v>
+        <v>0.02664458300930451</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>POS_CNT_RECORDS</t>
+          <t>INSTAL_MEAN_DAYS_LATE_WHEN_LATE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.001450924408373672</v>
+        <v>0.0261554042105636</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_2</t>
+          <t>NAME_EDUCATION_TYPE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.00140651160806084</v>
+        <v>0.02585553932232824</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RATE_DOWN_PAYMENT</t>
+          <t>POS_CNT_RECORDS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.001382792479716656</v>
+        <v>0.02574117627950871</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UPSTREAM_PD_FROM_NB01</t>
+          <t>OCCUPATION_TYPE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.001351697972287835</v>
+        <v>0.02487810305797875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>POS_CNT_COMPLETED</t>
+          <t>AMT_DOWN_PAYMENT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.001347296113493432</v>
+        <v>0.02459524336027134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAME_FAMILY_STATUS</t>
+          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.001304097142084249</v>
+        <v>0.02368475422806364</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CC_CNT_RECORDS</t>
+          <t>NAME_PRODUCT_TYPE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.001259778781395529</v>
+        <v>0.02239859917406555</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NAME_EDUCATION_TYPE</t>
+          <t>NAME_TYPE_SUITE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.001205480214634601</v>
+        <v>0.02214920799468265</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_CREDITS</t>
+          <t>RATE_DOWN_PAYMENT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001136766241118098</v>
+        <v>0.02172387673481738</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CC_MEAN_BALANCE</t>
+          <t>NAME_GOODS_CATEGORY</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.001133296669052778</v>
+        <v>0.01996108748336245</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CC_MEAN_UTILIZATION</t>
+          <t>NAME_CASH_LOAN_PURPOSE</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001088167704378858</v>
+        <v>0.01823873513379261</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OCCUPATION_TYPE</t>
+          <t>WEEKDAY_APPR_PROCESS_START</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.000953366220136083</v>
+        <v>0.01817108919388313</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WEEKDAY_APPR_PROCESS_START</t>
+          <t>NAME_PORTFOLIO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0008314673241089769</v>
+        <v>0.01779607879547744</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PRODUCT_COMBINATION</t>
+          <t>AMT_INCOME_TOTAL</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0007849620855900368</v>
+        <v>0.01767286732918805</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NAME_CASH_LOAN_PURPOSE</t>
+          <t>NAME_PAYMENT_TYPE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0007410986312304984</v>
+        <v>0.01686489613593433</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NAME_YIELD_GROUP</t>
+          <t>PRODUCT_COMBINATION</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0007378772526228718</v>
+        <v>0.01628442994486811</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NAME_PRODUCT_TYPE</t>
+          <t>NAME_CONTRACT_TYPE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0007041165461539884</v>
+        <v>0.01616183132178602</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NAME_TYPE_SUITE</t>
+          <t>CHANNEL_TYPE</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0006739261314690712</v>
+        <v>0.01581165226468986</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_ACTIVE</t>
+          <t>NAME_CLIENT_TYPE</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0006568475235175941</v>
+        <v>0.0157836500624944</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NAME_GOODS_CATEGORY</t>
+          <t>NAME_SELLER_INDUSTRY</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0006439258777485976</v>
+        <v>0.0152039289208659</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NAME_CONTRACT_TYPE</t>
+          <t>CC_MEAN_BALANCE</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.000555728543082132</v>
+        <v>0.01389821981985508</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NAME_PORTFOLIO</t>
+          <t>BUREAU_CNT_CREDITS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0005323446484587477</v>
+        <v>0.01159513192121732</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHANNEL_TYPE</t>
+          <t>BUREAU_TOTAL_DPD_MONTHS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0004859466886586141</v>
+        <v>0.01151982612977832</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NAME_SELLER_INDUSTRY</t>
+          <t>CC_MEAN_UTILIZATION</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0004608127377866733</v>
+        <v>0.01032932862428488</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BUREAU_TOTAL_DPD_MONTHS</t>
+          <t>NAME_YIELD_GROUP</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0004486618684941783</v>
+        <v>0.009883481485886837</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NAME_CLIENT_TYPE</t>
+          <t>CC_CNT_RECORDS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.000400284495254104</v>
+        <v>0.0096660455096987</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BUREAU_MAX_DAYS_OVERDUE</t>
+          <t>CC_SUM_SK_DPD</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0003467528263817063</v>
+        <v>0.00734222692998045</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NAME_PAYMENT_TYPE</t>
+          <t>BUREAU_MAX_DAYS_OVERDUE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0003373165811917935</v>
+        <v>0.006191930989888167</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CC_SUM_SK_DPD</t>
+          <t>BUREAU_CNT_ACTIVE</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0002662214458134613</v>
+        <v>0.005413292434753476</v>
       </c>
     </row>
   </sheetData>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1971.00 &lt; SELLERPLACE_AREA &lt;= 2991.75</t>
+          <t>SELLERPLACE_AREA &gt; 2991.75</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08079308255899306</v>
+        <v>0.2250740411048431</v>
       </c>
     </row>
     <row r="3">
@@ -2504,11 +2504,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16.00 &lt; INSTAL_CNT_PAYMENTS &lt;= 33.00</t>
+          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.009508061476372905</v>
+        <v>0.02611878533263995</v>
       </c>
     </row>
     <row r="4">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
+          <t>4069.72 &lt; AMT_ANNUITY &lt;= 6878.86</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.009294592745750868</v>
+        <v>0.01957107426567483</v>
       </c>
     </row>
     <row r="5">
@@ -2534,11 +2534,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60444.39 &lt; AMT_GOODS_PRICE &lt;= 98297.82</t>
+          <t>POS_CNT_RECORDS &gt; 18.00</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.009085874227624</v>
+        <v>0.01674456214034198</v>
       </c>
     </row>
     <row r="6">
@@ -2549,11 +2549,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POS_CNT_RECORDS &gt; 18.00</t>
+          <t>0.23 &lt; EXT_SOURCE_2 &lt;= 0.47</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007213419009146303</v>
+        <v>-0.01632309056045028</v>
       </c>
     </row>
     <row r="7">
@@ -2564,11 +2564,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMT_INCOME_TOTAL &lt;= 93813.02</t>
+          <t>NAME_PRODUCT_TYPE=2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.007187929306312578</v>
+        <v>-0.01626677599489742</v>
       </c>
     </row>
     <row r="8">
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.90 &lt; INSTAL_MEAN_PAYMENT_RATIO &lt;= 0.94</t>
+          <t>INSTAL_MEAN_DAYS_LATE_WHEN_LATE &gt; 10.40</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.006515811540301981</v>
+        <v>0.01439594469222996</v>
       </c>
     </row>
     <row r="9">
@@ -2594,11 +2594,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3298.00 &lt; BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL &lt;= 15890.25</t>
+          <t>HOUR_APPR_PROCESS_START &gt; 17.00</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006166826951900322</v>
+        <v>0.0136570534405174</v>
       </c>
     </row>
     <row r="10">
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.1442299911610529</v>
+        <v>-0.2764149188322492</v>
       </c>
     </row>
     <row r="11">
@@ -2624,11 +2624,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMT_APPLICATION &gt; 167994.88</t>
+          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.02389228278677951</v>
+        <v>0.0242178344026261</v>
       </c>
     </row>
     <row r="12">
@@ -2639,11 +2639,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMT_GOODS_PRICE &gt; 157856.14</t>
+          <t>CC_SUM_SK_DPD &lt;= 0.00</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02210686806112492</v>
+        <v>-0.01747820718296995</v>
       </c>
     </row>
     <row r="13">
@@ -2654,11 +2654,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMT_CREDIT &gt; 168517.18</t>
+          <t>BUREAU_AMT_CREDIT_SUM_TOTAL &gt; 315398.88</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.01604875205391277</v>
+        <v>-0.01640521407942242</v>
       </c>
     </row>
     <row r="14">
@@ -2669,11 +2669,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMT_ANNUITY &gt; 11499.33</t>
+          <t>CNT_PAYMENT &lt;= 21.00</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.01578204932525753</v>
+        <v>-0.01280239365952761</v>
       </c>
     </row>
     <row r="15">
@@ -2684,11 +2684,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
+          <t>INSTAL_MEAN_DAYS_LATE_WHEN_LATE &lt;= 0.00</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.009458343786281029</v>
+        <v>-0.01250379559715577</v>
       </c>
     </row>
     <row r="16">
@@ -2699,11 +2699,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60248.65 &lt; BUREAU_AMT_CREDIT_SUM_TOTAL &lt;= 157903.41</t>
+          <t>HOUR_APPR_PROCESS_START &lt;= 5.00</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.007547569873127417</v>
+        <v>0.01204035114140749</v>
       </c>
     </row>
     <row r="17">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INSTAL_MEAN_DAYS_LATE_WHEN_LATE &lt;= 0.00</t>
+          <t>NAME_PRODUCT_TYPE=2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.007189387848321779</v>
+        <v>-0.01190810159608673</v>
       </c>
     </row>
     <row r="18">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.14579288357062</v>
+        <v>-0.2807651891943753</v>
       </c>
     </row>
     <row r="19">
@@ -2744,11 +2744,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMT_APPLICATION &gt; 167994.88</t>
+          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.02536870562467125</v>
+        <v>0.02431166330412143</v>
       </c>
     </row>
     <row r="20">
@@ -2759,11 +2759,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMT_GOODS_PRICE &gt; 157856.14</t>
+          <t>AMT_ANNUITY &lt;= 4069.72</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.02239761908705978</v>
+        <v>-0.01682612865536089</v>
       </c>
     </row>
     <row r="21">
@@ -2774,11 +2774,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMT_CREDIT &gt; 168517.18</t>
+          <t>NAME_PRODUCT_TYPE=0</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.01908482984368292</v>
+        <v>0.01609969978634981</v>
       </c>
     </row>
     <row r="22">
@@ -2789,11 +2789,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4069.72 &lt; AMT_ANNUITY &lt;= 6878.86</t>
+          <t>POS_CNT_RECORDS &gt; 18.00</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.007945408018590875</v>
+        <v>0.01424466566236555</v>
       </c>
     </row>
     <row r="23">
@@ -2804,11 +2804,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CC_CNT_RECORDS &lt;= 0.00</t>
+          <t>AMT_APPLICATION &lt;= 56929.23</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.006969242756689381</v>
+        <v>0.01339451508308626</v>
       </c>
     </row>
     <row r="24">
@@ -2819,11 +2819,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAME_EDUCATION_TYPE=0</t>
+          <t>AMT_CREDIT &lt;= 57150.26</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.006837888458515907</v>
+        <v>0.01144691611443016</v>
       </c>
     </row>
     <row r="25">
@@ -2834,11 +2834,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
+          <t>0.23 &lt; EXT_SOURCE_2 &lt;= 0.47</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.006647903587278302</v>
+        <v>-0.0108377673220058</v>
       </c>
     </row>
   </sheetData>
